--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:14</t>
+    <t xml:space="preserve">2026-09-09 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:14</t>
+    <t xml:space="preserve">2026-09-17 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,26 +955,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>10.2</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11.08</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10.46</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="5">
@@ -1015,101 +1015,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10.77</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>10.2</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9.82</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11.83</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11.08</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11.26</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>10.83</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10.46</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9.76</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="11">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:41</t>
+    <t xml:space="preserve">2026-09-25 21:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -550,10 +550,10 @@
         <v>9.03</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.89</v>
+        <v>0.94</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>5</v>
@@ -573,10 +573,10 @@
         <v>10.08</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -599,7 +599,7 @@
         <v>-0.73</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5.47</v>
+        <v>-5.46</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>-0.57</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-5.29</v>
+        <v>-5.26</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -665,10 +665,10 @@
         <v>13.17</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.75</v>
+        <v>-0.74</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-5.69</v>
+        <v>-5.63</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -688,10 +688,10 @@
         <v>8.65</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1.97</v>
+        <v>-1.89</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>-0.42</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-3.89</v>
+        <v>-3.9</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
         <v>-0.74</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5.62</v>
+        <v>-5.59</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -757,10 +757,10 @@
         <v>8.49</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.56</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -780,10 +780,10 @@
         <v>10.83</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3.42</v>
+        <v>-3.36</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -829,7 +829,7 @@
         <v>0.14</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -849,10 +849,10 @@
         <v>11.83</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.75</v>
+        <v>-0.74</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-6.34</v>
+        <v>-6.28</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2023_aysen.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:40</t>
+    <t xml:space="preserve">2026-10-05 07:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
